--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486986_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486986_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7308</v>
+        <v>6.4344</v>
       </c>
       <c r="E2" t="n">
         <v>5.5902</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1407</v>
+        <v>0.8442</v>
       </c>
       <c r="G2" t="n">
         <v>4.3429</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7905</v>
+        <v>0.494</v>
       </c>
       <c r="T2" t="n">
         <v>0.1858</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6046</v>
+        <v>0.3082</v>
       </c>
       <c r="V2" t="n">
         <v>2.0082</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8325</v>
+        <v>5.0992</v>
       </c>
       <c r="E3" t="n">
         <v>4.8124</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0201</v>
+        <v>0.2868</v>
       </c>
       <c r="G3" t="n">
         <v>2.8914</v>
@@ -688,13 +688,13 @@
         <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7017</v>
+        <v>-0.4349</v>
       </c>
       <c r="T3" t="n">
         <v>0.12</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8216</v>
+        <v>-0.5548</v>
       </c>
       <c r="V3" t="n">
         <v>0.5893</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.564</v>
+        <v>2.7027</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2242</v>
+        <v>1.015</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3398</v>
+        <v>1.6877</v>
       </c>
       <c r="G4" t="n">
         <v>4.5224</v>
@@ -766,13 +766,13 @@
         <v>1.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8281</v>
+        <v>0.9667</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1467</v>
+        <v>0.9375</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6814</v>
+        <v>0.0293</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9384</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.173</v>
+        <v>2.5182</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2985</v>
+        <v>1.8215</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8746</v>
+        <v>0.6967</v>
       </c>
       <c r="G5" t="n">
         <v>1.1525</v>
@@ -844,13 +844,13 @@
         <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0636</v>
+        <v>0.4088</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1086</v>
+        <v>0.4144</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1722</v>
+        <v>-0.0057</v>
       </c>
       <c r="V5" t="n">
         <v>-0.4805</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4585</v>
+        <v>2.0983</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9139</v>
+        <v>3.2277</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4554</v>
+        <v>-1.1294</v>
       </c>
       <c r="G6" t="n">
         <v>3.2682</v>
@@ -922,13 +922,13 @@
         <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3909</v>
+        <v>0.249</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3216</v>
+        <v>-0.0078</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0693</v>
+        <v>0.2568</v>
       </c>
       <c r="V6" t="n">
         <v>-1.4189</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5707</v>
+        <v>0.2255</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2263</v>
+        <v>-0.2967</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3444</v>
+        <v>0.5222</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2063</v>
@@ -1000,13 +1000,13 @@
         <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4361</v>
+        <v>0.091</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0149</v>
+        <v>0.4919</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5788</v>
+        <v>-0.4009</v>
       </c>
       <c r="V7" t="n">
         <v>0.1088</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.1214</v>
       </c>
       <c r="E8" t="n">
         <v>0.5004999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4087</v>
+        <v>-0.3791</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0752</v>
@@ -1078,13 +1078,13 @@
         <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2437</v>
+        <v>-0.2141</v>
       </c>
       <c r="T8" t="n">
         <v>-0.124</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1197</v>
+        <v>-0.0901</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2381</v>
+        <v>-0.3957</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4425</v>
+        <v>1.6135</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6806</v>
+        <v>-2.0092</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1845</v>
+        <v>-1.4679</v>
       </c>
       <c r="H9" t="n">
-        <v>0.639</v>
+        <v>-0.4575</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8234</v>
+        <v>-1.0104</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5015</v>
+        <v>-0.2241</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3042</v>
+        <v>-0.2107</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1973</v>
+        <v>-0.0134</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.686</v>
+        <v>-1.2438</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6653</v>
+        <v>-0.2468</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0208</v>
+        <v>-0.997</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7348</v>
+        <v>0.0804</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8096</v>
+        <v>0.0696</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0747</v>
+        <v>0.0108</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.2259</v>
+        <v>-0.2402</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1314</v>
+        <v>1.7679</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3573</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0669</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0905</v>
+        <v>1.6057</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1574</v>
+        <v>-2.4731</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4679</v>
+        <v>-0.1845</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4575</v>
+        <v>0.639</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0104</v>
+        <v>-0.8234</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2241</v>
+        <v>1.5015</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2107</v>
+        <v>1.3042</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0134</v>
+        <v>0.1973</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2438</v>
+        <v>-1.686</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2468</v>
+        <v>-0.6653</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.997</v>
+        <v>-1.0208</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5908</v>
+        <v>0.1055</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4534</v>
+        <v>-0.0272</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1374</v>
+        <v>0.1328</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2402</v>
+        <v>-2.2259</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7679</v>
+        <v>0.1314</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.0082</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4056</v>
+        <v>-2.3166</v>
       </c>
       <c r="E11" t="n">
         <v>-1.5527</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8529</v>
+        <v>-0.7639</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3296</v>
@@ -1312,13 +1312,13 @@
         <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1561</v>
+        <v>0.245</v>
       </c>
       <c r="T11" t="n">
         <v>0.5152</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3591</v>
+        <v>-0.2702</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.656</v>
+        <v>-2.5654</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4114</v>
+        <v>-4.2022</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7554</v>
+        <v>1.6368</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0741</v>
@@ -1390,13 +1390,13 @@
         <v>1.8481</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6687</v>
+        <v>0.7594</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3912</v>
+        <v>0.6004</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2776</v>
+        <v>0.159</v>
       </c>
       <c r="V12" t="n">
         <v>2.0082</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.0547</v>
+        <v>13.0546</v>
       </c>
       <c r="E13" t="n">
-        <v>14.13489999999999</v>
+        <v>14.1349</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.080000000000001</v>
+        <v>-1.0803</v>
       </c>
       <c r="G13" t="n">
         <v>8.839800000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>7.104100000000001</v>
+        <v>7.1041</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7357</v>
+        <v>1.735699999999999</v>
       </c>
       <c r="J13" t="n">
         <v>16.8833</v>
@@ -1453,7 +1453,7 @@
         <v>-8.0435</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.993599999999999</v>
+        <v>-3.9936</v>
       </c>
       <c r="O13" t="n">
         <v>-4.050199999999999</v>
@@ -1468,16 +1468,16 @@
         <v>14.3741</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7508</v>
+        <v>2.750799999999999</v>
       </c>
       <c r="T13" t="n">
         <v>3.1758</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4247999999999999</v>
+        <v>-0.4248</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5894000000000004</v>
+        <v>-0.5893999999999999</v>
       </c>
       <c r="W13" t="n">
         <v>6.396100000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>G. KASANZI OBAMA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3914</v>
+        <v>1.0608</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4806</v>
+        <v>0.2715</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0892</v>
+        <v>0.7894</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.9072</v>
+        <v>1.6037</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.0497</v>
+        <v>1.2458</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8575</v>
+        <v>0.3579</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9032</v>
+        <v>2.5579</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9951</v>
+        <v>2.6897</v>
       </c>
       <c r="L14" t="n">
-        <v>0.092</v>
+        <v>-0.1318</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0041</v>
+        <v>-0.9542</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0546</v>
+        <v>-1.4439</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9495</v>
+        <v>0.4897</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.4641</v>
+        <v>-2.2588</v>
       </c>
       <c r="R14" t="n">
         <v>2.0534</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1734</v>
+        <v>0.0116</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7699</v>
+        <v>0.3214</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5965</v>
+        <v>-0.3098</v>
       </c>
       <c r="V14" t="n">
-        <v>3.5359</v>
+        <v>-0.3491</v>
       </c>
       <c r="W14" t="n">
-        <v>3.078</v>
+        <v>-0.3491</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. KASANZI OBAMA</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4541</v>
+        <v>0.8223</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0623</v>
+        <v>0.4931</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3919</v>
+        <v>0.3292</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6037</v>
+        <v>-2.9072</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2458</v>
+        <v>-2.0497</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3579</v>
+        <v>-0.8575</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5579</v>
+        <v>-0.9032</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6897</v>
+        <v>-0.9951</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1318</v>
+        <v>0.092</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9542</v>
+        <v>-2.0041</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4439</v>
+        <v>-1.0546</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4897</v>
+        <v>-0.9495</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2588</v>
+        <v>-2.4641</v>
       </c>
       <c r="R15" t="n">
         <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5951</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1122</v>
+        <v>0.7824</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7074</v>
+        <v>-0.1781</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3491</v>
+        <v>3.5359</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3491</v>
+        <v>3.078</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4798</v>
+        <v>-0.1747</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7851</v>
+        <v>-0.4713</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3053</v>
+        <v>0.2966</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8343</v>
@@ -1702,13 +1702,13 @@
         <v>0.616</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0561</v>
+        <v>0.249</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0581</v>
+        <v>0.2557</v>
       </c>
       <c r="U16" t="n">
-        <v>0.002</v>
+        <v>-0.0067</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.595</v>
+        <v>-0.1897</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.146</v>
+        <v>-0.6814</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.449</v>
+        <v>0.4917</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4741</v>
+        <v>-0.0075</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1427</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3314</v>
+        <v>0.0897</v>
       </c>
       <c r="J17" t="n">
-        <v>0.257</v>
+        <v>1.4334</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2175</v>
+        <v>0.7889</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0395</v>
+        <v>0.6445</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7311</v>
+        <v>-1.4408</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3602</v>
+        <v>-0.886</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3709</v>
+        <v>-0.5548</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2053</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2053</v>
+        <v>-3.4908</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4107</v>
+        <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3262</v>
+        <v>0.4872</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1976</v>
+        <v>-0.0428</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1286</v>
+        <v>0.53</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>E. ORTIZ TORRES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.2781</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4136</v>
+        <v>1.6633</v>
       </c>
       <c r="F18" t="n">
-        <v>0.776</v>
+        <v>-1.9414</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0075</v>
+        <v>1.3093</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.1752</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0897</v>
+        <v>1.1342</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4334</v>
+        <v>3.0582</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7889</v>
+        <v>1.2298</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6445</v>
+        <v>1.8285</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4408</v>
+        <v>-1.7489</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.886</v>
+        <v>-1.0546</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5548</v>
+        <v>-0.6943</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8481</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4908</v>
+        <v>-1.4374</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0393</v>
+        <v>-0.1685</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.775</v>
+        <v>0.0425</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8143</v>
+        <v>-0.211</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1786</v>
+        <v>-1.4189</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2402</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ORTIZ TORRES</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.223</v>
+        <v>-0.5148</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0357</v>
+        <v>-0.146</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2587</v>
+        <v>-0.3688</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3093</v>
+        <v>-0.4741</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1752</v>
+        <v>-0.1427</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1342</v>
+        <v>-0.3314</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0582</v>
+        <v>0.257</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2298</v>
+        <v>0.2175</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8285</v>
+        <v>0.0395</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7489</v>
+        <v>-0.7311</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0546</v>
+        <v>-0.3602</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6943</v>
+        <v>-0.3709</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.4374</v>
+        <v>-0.2053</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1135</v>
+        <v>-0.246</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5851</v>
+        <v>-0.1976</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5284</v>
+        <v>-0.0484</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7433</v>
+        <v>-2.3981</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2623</v>
+        <v>-1.0944</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.481</v>
+        <v>-1.3037</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9292</v>
+        <v>-1.4591</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8005</v>
+        <v>-1.7066</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1287</v>
+        <v>0.2475</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5566</v>
+        <v>0.1688</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6355</v>
+        <v>-0.5416</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0789</v>
+        <v>0.7104</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3726</v>
+        <v>-1.6278</v>
       </c>
       <c r="N20" t="n">
         <v>-1.1649</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2077</v>
+        <v>-0.4629</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.616</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0422</v>
+        <v>-0.3497</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0808</v>
+        <v>-0.2364</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0386</v>
+        <v>-0.1132</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2402</v>
+        <v>-0.5893</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.4805</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2925</v>
+        <v>-2.4407</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3036</v>
+        <v>-1.0991</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9889</v>
+        <v>-1.3416</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4591</v>
+        <v>-1.9292</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7066</v>
+        <v>-1.8005</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2475</v>
+        <v>-0.1287</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1688</v>
+        <v>-0.5566</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5416</v>
+        <v>-0.6355</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7104</v>
+        <v>0.0789</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6278</v>
+        <v>-1.3726</v>
       </c>
       <c r="N21" t="n">
         <v>-1.1649</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4629</v>
+        <v>-0.2077</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.616</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2441</v>
+        <v>0.3448</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4457</v>
+        <v>0.244</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7984</v>
+        <v>0.1008</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5893</v>
+        <v>-0.2402</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5893</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>J. PARRA BAEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7938</v>
+        <v>-2.8015</v>
       </c>
       <c r="E22" t="n">
-        <v>2.921</v>
+        <v>-0.8812</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.7147</v>
+        <v>-1.9203</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0386</v>
+        <v>-4.1027</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8199</v>
+        <v>0.1523</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7813</v>
+        <v>-4.255</v>
       </c>
       <c r="J22" t="n">
-        <v>3.0283</v>
+        <v>-0.4785</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.655</v>
+        <v>2.4561</v>
       </c>
       <c r="L22" t="n">
-        <v>3.6834</v>
+        <v>-2.9346</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.067</v>
+        <v>-3.6242</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1649</v>
+        <v>-2.3038</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.902</v>
+        <v>-1.3204</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
-        <v>0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.555</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6433</v>
+        <v>-0.2055</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1386</v>
+        <v>-0.3495</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.3573</v>
+        <v>0.8295</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7679</v>
+        <v>0.8295</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.1252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. PARRA BAEZ</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1352</v>
+        <v>-3.3509</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5088</v>
+        <v>3.0256</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6264</v>
+        <v>-6.3765</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.1027</v>
+        <v>-0.0386</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1523</v>
+        <v>-1.8199</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.255</v>
+        <v>1.7813</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4785</v>
+        <v>3.0283</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4561</v>
+        <v>-0.655</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.9346</v>
+        <v>3.6834</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.6242</v>
+        <v>-3.067</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.3038</v>
+        <v>-1.1649</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3204</v>
+        <v>-1.902</v>
       </c>
       <c r="P23" t="n">
-        <v>1.0267</v>
+        <v>-0.616</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0534</v>
+        <v>0.616</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8887</v>
+        <v>-0.339</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.5387</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0556</v>
+        <v>0.1996</v>
       </c>
       <c r="V23" t="n">
-        <v>0.8295</v>
+        <v>-2.3573</v>
       </c>
       <c r="W23" t="n">
-        <v>0.8295</v>
+        <v>1.7679</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-4.1252</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.0547</v>
+        <v>-10.2654</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0802</v>
+        <v>1.0801</v>
       </c>
       <c r="F24" t="n">
-        <v>-14.1347</v>
+        <v>-11.3454</v>
       </c>
       <c r="G24" t="n">
         <v>-8.839700000000001</v>
@@ -2326,16 +2326,16 @@
         <v>12.3204</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.750599999999999</v>
+        <v>0.03869999999999979</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4248999999999997</v>
+        <v>0.425</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.1758</v>
+        <v>-0.3862999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5892000000000001</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="W24" t="n">
         <v>6.9854</v>
